--- a/OrangeHRM/Data/OrangeHRM_Login.xlsx
+++ b/OrangeHRM/Data/OrangeHRM_Login.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29922"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Life\Learning\Esprit\PFE\Project\TessanTIS\TessanTIS.OrangeHRM.Data.Impl\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Life\Learning\Esprit\PFE\Project\TessanTIS\OrangeHRM\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E92A803-B951-415C-B64F-A73585DBE19E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CBC6BA9-5198-48A6-A0E4-85235C2EC9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-6540" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{56F28EB9-5BA8-428B-AB16-A5C338242BCA}"/>
+    <workbookView xWindow="28680" yWindow="-6540" windowWidth="29040" windowHeight="15720" xr2:uid="{56F28EB9-5BA8-428B-AB16-A5C338242BCA}"/>
   </bookViews>
   <sheets>
     <sheet name="OrangeHRM_Login_TC001" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="42">
   <si>
     <t>Steps</t>
   </si>
@@ -157,6 +157,12 @@
   </si>
   <si>
     <t>There are 8 errors</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>admin123</t>
   </si>
 </sst>
 </file>
@@ -590,10 +596,10 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
@@ -825,12 +831,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1037,15 +1040,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4EF81E7-E39B-43E7-BD54-614E952B9C15}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E949F8F-1265-4F7D-8B3B-442451397EE3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1070,10 +1077,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E949F8F-1265-4F7D-8B3B-442451397EE3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4EF81E7-E39B-43E7-BD54-614E952B9C15}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/OrangeHRM/Data/OrangeHRM_Login.xlsx
+++ b/OrangeHRM/Data/OrangeHRM_Login.xlsx
@@ -8,14 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Life\Learning\Esprit\PFE\Project\TessanTIS\OrangeHRM\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CBC6BA9-5198-48A6-A0E4-85235C2EC9B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{540664A4-976E-4F50-A9C4-84BE235778CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-6540" windowWidth="29040" windowHeight="15720" xr2:uid="{56F28EB9-5BA8-428B-AB16-A5C338242BCA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{56F28EB9-5BA8-428B-AB16-A5C338242BCA}"/>
   </bookViews>
   <sheets>
     <sheet name="OrangeHRM_Login_TC001" sheetId="1" r:id="rId1"/>
-    <sheet name="OrangeHRM_Login_TC002" sheetId="2" r:id="rId2"/>
-    <sheet name="OrangeHRM_Login_TC003" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Steps</t>
   </si>
@@ -48,93 +46,18 @@
     <t>Password</t>
   </si>
   <si>
-    <t>CreateAccountEmail</t>
-  </si>
-  <si>
-    <t>Gender</t>
-  </si>
-  <si>
-    <t>CustomerFirstName</t>
-  </si>
-  <si>
-    <t>CustomerLastName</t>
-  </si>
-  <si>
-    <t>NewPassword</t>
-  </si>
-  <si>
-    <t>Company</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>PostCode</t>
-  </si>
-  <si>
-    <t>PhoneNumber</t>
-  </si>
-  <si>
-    <t>Alias</t>
-  </si>
-  <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>Country</t>
-  </si>
-  <si>
-    <t>Adress</t>
-  </si>
-  <si>
     <t>Step 1</t>
   </si>
   <si>
-    <t>test</t>
-  </si>
-  <si>
     <t>Step 2</t>
   </si>
   <si>
     <t>Step 3</t>
   </si>
   <si>
-    <t>hamza.benguirat@esprit.tn</t>
-  </si>
-  <si>
     <t>Step 4</t>
   </si>
   <si>
-    <t>Mr.</t>
-  </si>
-  <si>
-    <t>Hamza</t>
-  </si>
-  <si>
-    <t>BEN GUIRAT</t>
-  </si>
-  <si>
-    <t>Test123456!</t>
-  </si>
-  <si>
-    <t>Tessan</t>
-  </si>
-  <si>
-    <t>TestCity</t>
-  </si>
-  <si>
-    <t>test tes</t>
-  </si>
-  <si>
-    <t>Alabama</t>
-  </si>
-  <si>
-    <t>United States</t>
-  </si>
-  <si>
-    <t>Test adress</t>
-  </si>
-  <si>
     <t>Step 5</t>
   </si>
   <si>
@@ -142,21 +65,6 @@
   </si>
   <si>
     <t>Step 7</t>
-  </si>
-  <si>
-    <t>ErrorMessage</t>
-  </si>
-  <si>
-    <t>hamza.benguirat</t>
-  </si>
-  <si>
-    <t>Invalid email address.</t>
-  </si>
-  <si>
-    <t>EmptyFieldsErrorMessage</t>
-  </si>
-  <si>
-    <t>There are 8 errors</t>
   </si>
   <si>
     <t>Admin</t>
@@ -531,7 +439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2223E30E-CC8E-4585-A018-9A29E0B468FB}">
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" bestFit="1" customWidth="1"/>
@@ -541,7 +449,7 @@
     <col min="12" max="12" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -551,281 +459,51 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5">
-        <v>10000</v>
-      </c>
-      <c r="L5">
-        <v>123456789</v>
-      </c>
-      <c r="M5" t="s">
-        <v>28</v>
-      </c>
-      <c r="N5" t="s">
-        <v>29</v>
-      </c>
-      <c r="O5" t="s">
-        <v>30</v>
-      </c>
-      <c r="P5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1" xr:uid="{899B7027-2402-4CFD-A72B-1CC68DC9F67D}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2C918F3-AD65-48D4-81A7-7A4957BA230E}">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1" xr:uid="{5730DFCF-B1AE-4499-9055-9AD2FDB0FBD0}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B91F914-4D7D-4844-89EF-B88CE27B94AD}">
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1" xr:uid="{8881BB00-0F99-4CD8-9092-4C8B6A1181C8}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -837,6 +515,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C1D9689BC10D74FBDB569E6E80ED286" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="e193ee76a93e1a439b3cae51403dd597">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c494e978-fd52-4122-96f3-83d7c94282c9" xmlns:ns4="b9756793-60a6-4e91-b93f-ed15f553695a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3f59eb8f914e4cb4e3fda9f0b6e41ab4" ns3:_="" ns4:_="">
     <xsd:import namespace="c494e978-fd52-4122-96f3-83d7c94282c9"/>
@@ -1039,15 +726,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E949F8F-1265-4F7D-8B3B-442451397EE3}">
   <ds:schemaRefs>
@@ -1058,6 +736,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4EF81E7-E39B-43E7-BD54-614E952B9C15}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BCA388CD-F2B6-42EB-8847-A12F80FD17BC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1074,12 +760,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4EF81E7-E39B-43E7-BD54-614E952B9C15}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>